--- a/output/第10期計画_介護給付費分科会資料（原典）の受領点検.xlsx
+++ b/output/第10期計画_介護給付費分科会資料（原典）の受領点検.xlsx
@@ -567,7 +567,7 @@
     <row r="2" ht="56" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>令和8年10月14日に受領した社会保障審議会介護給付費分科会の資料11件（全311頁）を、当方の計画素案及びサービス見込量の算定と突き合わせたものです。基準日 令和8年10月14日。</t>
+          <t>令和8年10月14日に受領した社会保障審議会介護給付費分科会の資料25件（全1037頁）を、当方の計画素案及びサービス見込量の算定と突き合わせたものです。基準日 令和8年10月14日。</t>
         </is>
       </c>
     </row>
@@ -608,7 +608,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>第268回 資料1（基本的な視点（案）及び概要）、第269回 資料1から資料4、第270回 資料1から資料5の11件・全311頁。いずれも資料の表紙に回・資料番号・開催日の記載があります。</t>
+          <t>第268回 資料1（基本的な視点（案）及び概要）、第269回 資料1から資料4、第270回 資料1から資料5の25件・全1037頁。いずれも資料の表紙に回・資料番号・開催日の記載があります。</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>5件</t>
+          <t>9件</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
@@ -734,7 +734,7 @@
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>14件</t>
+          <t>26件</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
@@ -809,7 +809,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H23"/>
+  <dimension ref="A1:H40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -825,7 +825,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>受領した原典（11件・全311頁）</t>
+          <t>受領した原典（25件・全1037頁）</t>
         </is>
       </c>
     </row>
@@ -1293,162 +1293,790 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="24" customHeight="1">
-      <c r="A16" s="11" t="inlineStr"/>
-      <c r="B16" s="11" t="inlineStr"/>
-      <c r="C16" s="11" t="inlineStr"/>
-      <c r="D16" s="11" t="inlineStr"/>
-      <c r="E16" s="11" t="inlineStr">
-        <is>
-          <t>計</t>
-        </is>
-      </c>
-      <c r="F16" s="12" t="inlineStr">
-        <is>
-          <t>11件</t>
-        </is>
-      </c>
-      <c r="G16" s="13" t="n">
-        <v>311</v>
-      </c>
-      <c r="H16" s="11" t="inlineStr"/>
-    </row>
-    <row r="17"/>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>会議の開催日との照合</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="4" t="inlineStr"/>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>回</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>開催日（整理）</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>開催日（原典）</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>判定</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>主な議題（整理による）</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="inlineStr"/>
-      <c r="H19" s="4" t="inlineStr"/>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>001733553</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>第262回</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>資料1</t>
+        </is>
+      </c>
+      <c r="E16" s="9" t="inlineStr">
+        <is>
+          <t>R8.8.5</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>定期巡回・随時対応型訪問介護看護及び夜間対応型訪問介護</t>
+        </is>
+      </c>
+      <c r="G16" s="10" t="n">
+        <v>65</v>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>現状と課題及び論点</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>001753395</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>第262回</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="inlineStr">
+        <is>
+          <t>資料2</t>
+        </is>
+      </c>
+      <c r="E17" s="9" t="inlineStr">
+        <is>
+          <t>R8.8.5</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>高齢者住まいに対するサービス提供の在り方</t>
+        </is>
+      </c>
+      <c r="G17" s="10" t="n">
+        <v>87</v>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>現状と課題及び論点（2件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>001733555</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>第262回</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>資料3</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="inlineStr">
+        <is>
+          <t>R8.8.5</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>地域区分</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="n">
+        <v>18</v>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>現状と課題及び論点</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="26" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>001733556</t>
+        </is>
+      </c>
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>第262回</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>資料4</t>
+        </is>
+      </c>
+      <c r="E19" s="9" t="inlineStr">
+        <is>
+          <t>R8.8.5</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>令和9年度介護報酬改定に関する意見交換会・実施要領について（案）</t>
+        </is>
+      </c>
+      <c r="G19" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>実施方法・テーマ4区分・実施団体</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="26" customHeight="1">
       <c r="A20" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B20" s="9" t="inlineStr">
-        <is>
-          <t>第268回</t>
+        <v>16</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>001743314</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>R8.9.30</t>
+          <t>第263回</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>R8.9.30</t>
-        </is>
-      </c>
-      <c r="E20" s="14" t="inlineStr">
-        <is>
-          <t>一致</t>
+          <t>資料1</t>
+        </is>
+      </c>
+      <c r="E20" s="9" t="inlineStr">
+        <is>
+          <t>R8.8.28</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>改定に関する基本的な視点（案）5つの視点</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr"/>
-      <c r="H20" s="5" t="inlineStr"/>
+          <t>介護人材確保に向けた処遇改善等</t>
+        </is>
+      </c>
+      <c r="G20" s="10" t="n">
+        <v>66</v>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>現状と課題及び論点</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="26" customHeight="1">
       <c r="A21" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>第269回</t>
+        <v>17</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>001743315</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>R8.10.9</t>
+          <t>第263回</t>
         </is>
       </c>
       <c r="D21" s="9" t="inlineStr">
         <is>
-          <t>R8.10.9</t>
-        </is>
-      </c>
-      <c r="E21" s="14" t="inlineStr">
-        <is>
-          <t>一致</t>
+          <t>資料2</t>
+        </is>
+      </c>
+      <c r="E21" s="9" t="inlineStr">
+        <is>
+          <t>R8.8.28</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>定期巡回・小多機・看多機等の具体的対応案</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr"/>
-      <c r="H21" s="5" t="inlineStr"/>
+          <t>介護現場の生産性向上等の推進</t>
+        </is>
+      </c>
+      <c r="G21" s="10" t="n">
+        <v>78</v>
+      </c>
+      <c r="H21" s="5" t="inlineStr">
+        <is>
+          <t>現状と課題及び論点</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="26" customHeight="1">
       <c r="A22" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>001743316</t>
+        </is>
+      </c>
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>第263回</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>資料3</t>
+        </is>
+      </c>
+      <c r="E22" s="9" t="inlineStr">
+        <is>
+          <t>R8.8.28</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>高齢者虐待の防止／介護現場における安全性の確保、リスクマネジメント</t>
+        </is>
+      </c>
+      <c r="G22" s="10" t="n">
+        <v>61</v>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>現状と課題及び論点（2件）</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="26" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>001743317</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>第263回</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>資料4</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>R8.8.28</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>災害時等における業務継続の取組の強化等</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>現状と課題及び論点</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>001743318</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>第263回</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>資料5</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>R8.8.28</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>介護現場におけるハラスメント対策</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="n">
+        <v>44</v>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>現状と課題及び論点</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>001744916</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>第264回</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>資料1</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>R8.9.3</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>認知症への対応力強化</t>
+        </is>
+      </c>
+      <c r="G25" s="10" t="n">
+        <v>60</v>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>現状と課題及び論点</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>001744917</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>第264回</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="inlineStr">
+        <is>
+          <t>資料2</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>R8.9.3</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>医療・介護連携、人生の最終段階の医療・介護</t>
+        </is>
+      </c>
+      <c r="G26" s="10" t="n">
+        <v>72</v>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>現状と課題及び論点</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="26" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>001744922</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>第264回</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="inlineStr">
+        <is>
+          <t>資料3</t>
+        </is>
+      </c>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>R8.9.3</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>科学的介護情報システム（LIFE）</t>
+        </is>
+      </c>
+      <c r="G27" s="10" t="n">
+        <v>41</v>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>現状と課題及び論点</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="26" customHeight="1">
+      <c r="A28" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>001744920</t>
+        </is>
+      </c>
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>第264回</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="inlineStr">
+        <is>
+          <t>資料4</t>
+        </is>
+      </c>
+      <c r="E28" s="9" t="inlineStr">
+        <is>
+          <t>R8.9.3</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>口腔・栄養、一体的取組</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="n">
+        <v>79</v>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>現状と課題及び論点</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="26" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>001744921</t>
+        </is>
+      </c>
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>第264回</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="inlineStr">
+        <is>
+          <t>資料5</t>
+        </is>
+      </c>
+      <c r="E29" s="9" t="inlineStr">
+        <is>
+          <t>R8.9.3</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>多床室の室料負担</t>
+        </is>
+      </c>
+      <c r="G29" s="10" t="n">
+        <v>22</v>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>現状と課題及び論点</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="11" t="inlineStr"/>
+      <c r="B30" s="11" t="inlineStr"/>
+      <c r="C30" s="11" t="inlineStr"/>
+      <c r="D30" s="11" t="inlineStr"/>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>計</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>25件</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="n">
+        <v>1037</v>
+      </c>
+      <c r="H30" s="11" t="inlineStr"/>
+    </row>
+    <row r="31"/>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>会議の開催日との照合</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="4" t="inlineStr"/>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>回</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>開催日（整理）</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>開催日（原典）</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>判定</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>主な議題（整理による）</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34" ht="26" customHeight="1">
+      <c r="A34" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>第262回</t>
+        </is>
+      </c>
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>R8.8.5</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="inlineStr">
+        <is>
+          <t>R8.8.5</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>定期巡回・夜間対応、住まい、地域区分</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="5" t="inlineStr"/>
+    </row>
+    <row r="35" ht="26" customHeight="1">
+      <c r="A35" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>第263回</t>
+        </is>
+      </c>
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>R8.8.28</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>R8.8.28</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>人材、処遇、生産性、虐待・安全、BCP、ハラスメント</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="5" t="inlineStr"/>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>第264回</t>
+        </is>
+      </c>
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>R8.9.3</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="inlineStr">
+        <is>
+          <t>R8.9.3</t>
+        </is>
+      </c>
+      <c r="E36" s="14" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>認知症、医療連携、LIFE、口腔栄養、室料負担</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="5" t="inlineStr"/>
+    </row>
+    <row r="37" ht="26" customHeight="1">
+      <c r="A37" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B37" s="9" t="inlineStr">
+        <is>
+          <t>第268回</t>
+        </is>
+      </c>
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>R8.9.30</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="inlineStr">
+        <is>
+          <t>R8.9.30</t>
+        </is>
+      </c>
+      <c r="E37" s="14" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>改定に関する基本的な視点（案）5つの視点</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr"/>
+      <c r="H37" s="5" t="inlineStr"/>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B38" s="9" t="inlineStr">
+        <is>
+          <t>第269回</t>
+        </is>
+      </c>
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>R8.10.9</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>R8.10.9</t>
+        </is>
+      </c>
+      <c r="E38" s="14" t="inlineStr">
+        <is>
+          <t>一致</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>定期巡回・小多機・看多機等の具体的対応案</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="5" t="inlineStr"/>
+    </row>
+    <row r="39" ht="26" customHeight="1">
+      <c r="A39" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
         <is>
           <t>第270回</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C39" s="9" t="inlineStr">
         <is>
           <t>R8.10.14</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
+      <c r="D39" s="9" t="inlineStr">
         <is>
           <t>R8.10.14</t>
         </is>
       </c>
-      <c r="E22" s="14" t="inlineStr">
+      <c r="E39" s="14" t="inlineStr">
         <is>
           <t>一致</t>
         </is>
       </c>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>通所・リハ・短期入所の具体案</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-    </row>
-    <row r="23" ht="36" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr"/>
+      <c r="H39" s="5" t="inlineStr"/>
+    </row>
+    <row r="40" ht="36" customHeight="1">
+      <c r="A40" s="8" t="inlineStr">
         <is>
           <t>注）原典の開催日は資料の表紙の記載によります。第256回から第267回までの資料は受領していないため、整理による開催日を原典で確かめていません。</t>
         </is>
@@ -1456,9 +2084,9 @@
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A32:H32"/>
     <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A40:H40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1470,7 +2098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1484,7 +2112,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>原典による確認（7件）</t>
+          <t>原典による確認（11件）</t>
         </is>
       </c>
     </row>
@@ -1710,32 +2338,152 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
+          <t>I28</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>給付・負担／地域区分・多床室の室料負担</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="inlineStr">
+        <is>
+          <t>詳細判明</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>地域区分は公務員の地域手当に準拠して設定され、地域手当は10年ごとに見直される。令和6年人事院勧告により級地区分を設定する地域の単位を都道府県単位を基本として広域化し段階数を7区分から5区分とする見直しが示されたことを踏まえ、令和9年度改定における対応が論点とされている。特例に広域連合ルールがある（G17）。多床室の室料負担は令和7年8月から一部の類型について既に実施されており、検討されているのは見送られた類型への拡大である（G23）。</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>第6章第6節2、第6章第7節</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="108" customHeight="1">
+      <c r="A12" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>I23</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>医療連携／協力医療機関・感染症・看取り</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>詳細判明</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>協力医療機関の設定の義務化には令和9年3月31日までの経過措置が設けられている。全国における要件を満たす体制の整備割合は介護老人福祉施設67.9％・介護老人保健施設83.3％・介護医療院84.9％であり、定めの状況を集計していないと回答した自治体が一定程度存在する（G22）。感染対応力の向上、ＡＣＰ、看取りも論点とされている。</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>第1章第9節1、第6章第4節</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="108" customHeight="1">
+      <c r="A13" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>I02</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>経営・人材／物価対応・処遇改善と経営の持続性</t>
+        </is>
+      </c>
+      <c r="D13" s="15" t="inlineStr">
+        <is>
+          <t>詳細判明</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>令和8年度介護報酬改定は令和8年6月施行であり、介護従事者を対象とした幅広い措置に加え、生産性向上等に取り組む事業者の介護職員を対象とした上乗せ措置が実施されている（G26）。処遇改善加算の取得の進展を踏まえた対応と報酬体系の簡素化が論点とされている。</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>第2章第6節、第5章 基本目標4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="108" customHeight="1">
+      <c r="A14" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>I03</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>経営・人材／生産性向上とサービスの質</t>
+        </is>
+      </c>
+      <c r="D14" s="15" t="inlineStr">
+        <is>
+          <t>詳細判明</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>生産性向上について、夜間の見守り機器の活用による方策、生産性向上推進体制加算の評価の在り方及び訪問系・通所系の取組の評価、経営の協働化・大規模化の推進が論点とされている（G20）。</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>第1章第9節1、第5章 基本目標4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="108" customHeight="1">
+      <c r="A15" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
           <t>I19</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>施設・住まい／特別養護老人ホームの重度者対応</t>
         </is>
       </c>
-      <c r="D11" s="15" t="inlineStr">
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t>詳細判明</t>
         </is>
       </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>「通所介護及び地域密着型通所介護の1事業所あたり利用者数は、通所介護は50.5人、地域密着型通所介護は24.6人」であり、中重度者ケア体制加算の配置要件が同一であることを踏まえ、「地域密着型通所介護の中重度者ケア体制加算について、小規模事業所の経営や人材確保の観点から、算定要件の見直し」が対応案として示されている。</t>
         </is>
       </c>
-      <c r="F11" s="5" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>第6章第4節2、第6章第5節</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="36" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+    <row r="16" ht="36" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>注）出所は原典の記述の要点欄に示した回及び資料番号によります。原典の記述は要点を示したものであり、原文そのままではありません。</t>
         </is>
@@ -1744,7 +2492,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A16:F16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1885,7 +2633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1900,7 +2648,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>原典により新たに分かったもの（14件）</t>
+          <t>原典により新たに分かったもの（26件）</t>
         </is>
       </c>
     </row>
@@ -2406,37 +3154,457 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
+          <t>G15</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>登録施設介護（予防）支援及び有料老人ホームの登録制の施行日</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>第262回 資料2 p22</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>社会福祉法等の一部を改正する法律の附則により、有料老人ホームの登録制の施行日は「公布の日から起算して二年を超えない範囲内において政令で定める日」であり、施行日に現に有料老人ホームを設置している者は「第三号施行日から起算して一年六月を超えない範囲内において政令で定める日までの間」は登録を受けないで事業を行うことができる。また「（参考）登録施設介護（予防）支援の創設に係る施行日は、公布日から起算して3年を超えない範囲において政令で定める日」とされている。公布は令和8年6月25日である。</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>**当方は計画素案に「令和9年4月1日に新設される登録施設介護（予防）支援」と書いていた。** 改正法の施行は原則として令和9年4月1日であるが、登録制及び登録施設介護（予防）支援はこれに当たらない。区域内には住宅型有料老人ホーム9施設（定員223人）があり、登録施設介護（予防）支援の対象となり得る方がいる。</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>第1章第9節2、第6章第2節 注3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="104" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>G16</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>同一建物等居住者へのサービス提供の実態</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>第262回 資料2 p53・p80・p87</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>「同一建物等居住者へのサービス提供割合が多くなるにつれて、訪問件数は増加し、移動時間や移動距離は短くなっている実態」。全国の住宅型有料老人ホームでは「要介護者のうち週21回以上（1日平均3回以上）訪問介護を利用している入居者の割合の平均は27.7％」であり、「比較的状態像の軽い要介護1，2でも週21回以上訪問介護を利用している者が、住宅型で18.5％」。併設又は隣接の介護等事業所がある住宅型有料老人ホームは79.1％、サービス付き高齢者向け住宅（非特定施設）は83.4％。論点は「経営実態やサービス提供実態を丁寧に把握した上で、その実態に合わせた必要な見直しを検討すること」である。</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>当区域の訪問介護の1人1月あたり利用回数は全国の1.87倍であり、訪問介護13事業所のうち8事業所が住まいに併設している。**当方の仮説（指定を受けない住まいの入居者への訪問による）は国の資料が示す実態と同じ向きである。**同一の建物に居住する方への提供の割合は把握していない。</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>第2章第3節、第1章第9節6</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="104" customHeight="1">
+      <c r="A20" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>G17</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>地域区分の広域連合ルールと令和9年度改定における見直し</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>第262回 資料3 p6・p7・p18</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>地域区分の特例に「ウ　**広域連合については、構成自治体に適用されている区分の範囲内で選択することを認めている**」がある（広域連合ルール）。また「国家公務員の地域手当については、令和6年人事院勧告において、級地区分を設定する地域の単位を広域化（従来の市町村単位から都道府県単位を基本）するとともに、級地区分の段階数を7区分から5区分とする見直し内容が示され」たことを踏まえ、「令和9年度介護報酬改定における対応についてどのように考えるか」が論点とされている。令和6年度から令和8年度までの適用地域の表において、北海道で級地が設定されているのは札幌市のみである。</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>**構成3町はいずれも表に現れず、その他の地域（上乗せ割合0％）である。**3町の区分が同じであるため、現時点では広域連合として選択する余地はない。都道府県単位を基本とする広域化が行われる場合は上乗せ割合が変わり得るため、単価に及ぶ。当方は地域区分について「令和7年度の実績に含まれています」と書くにとどめていた。</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>第1章第9節6、第6章第6節2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="104" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>G18</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>業務継続に係る市町村の助言等の状況</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>第263回 資料4 p30・p31</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>「BCPの実効性を高めるためには、行政や他の介護施設等との平時からの連携が重要と考えられるが、…**市区町村においても介護事業所等に対して、業務継続を可能とする備えに関する助言等を約6割が行っていない状況**にあり、平時における行政や近隣の法人等の連携体制の整備が課題となっている」。「災害時情報共有システムを知らない施設等が2割あり、運用に関する取組を行っていない施設等も3割ある」。論点は「災害対策基本法等の改正などを踏まえた災害発生時に備えた平時からの行政や他の介護施設等との連携による体制整備を促進するための方策」である。</t>
+        </is>
+      </c>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>**助言等を行うのは保険者及び構成3町の側である。**当方の素案はBCPの策定率・訓練・相互応援協定の把握を掲げていたが、行政の側の役割（助言・平時からの連携体制の整備・災害時情報共有システムの運用）に触れていなかった。</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>第5章 基本目標5</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="104" customHeight="1">
+      <c r="A22" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>G19</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>認知症及び軽度認知障害の将来の見通し</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>第264回 資料1 p59</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>「認知症高齢者数は、令和4年で約443万人、軽度認知障害（MCI）高齢者数は約559万人と推計され、その合計は1,000万人を超える状況にある。また、**令和22年にはその人数が約1,200万人（認知症約584万人、MCI約613万人）となり、高齢者の約3.3人に1人が認知症又はMCIになると見込まれる**」。「独居認知症高齢者と独居MCI高齢者を合算した独居認知機能低下高齢者は、2025年の段階で250万人、2050年には349万人になると推計」。「令和2年調査における若年性認知症の人の数は約3.6万人」。</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>当区域の認知症高齢者の日常生活自立度Ⅱ以上は令和6年10月末1,498人（認定者の60.3％）であり、軽度認知障害を含む割合及び独居の状況は把握していない。</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>第2章第1節3</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="104" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>G20</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>生産性向上の論点（夜間の見守り機器・経営の協働化）</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>第263回 資料2 p78</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>論点は「特に夜間の見守り機器の活用による職員の業務時間の削減等が見られたことを踏まえ、夜間の見守り機器を活用した場合の方策」と、「令和6年に新設した施設系サービスの生産性向上推進体制加算について先進的な取組への評価のあり方や訪問系・通所系サービスの生産性向上の取組の評価等」、及び「地域の実情等を踏まえた**経営の協働化・大規模化の推進**」である。</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>区域内の事業所の運営法人は28法人であり、1事業所のみを運営する法人が13ある。協働化は社会福祉法等改正法による都道府県との協定とも関わる（第1章第9節5）。</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>第2章第6節、第5章 基本目標4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="104" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>G22</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>協力医療機関の定めの状況を集計していない自治体があること</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>第264回 資料2 p70・p72</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>「令和6年度介護報酬改定において、高齢者施設等に一定の要件を満たす協力医療機関の設定を義務付け、**令和9年3月31日までの経過措置**を設けている」。「協力医療機関の要件を満たす体制の整備割合は、介護老人福祉施設は67.9％、介護老人保健施設は83.3％、介護医療院は84.9％、養護老人ホームは60.4％であり、また、**定めの状況について、集計していないと回答した自治体が一定程度存在し、定めの状況には地域差が見られた**」。協力医療機関となることを断った理由として「常時診療を行う体制の確保が困難」等が挙げられている。令和8年度改定検証調査の速報値は令和8年秋頃に示される予定。</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>**経過措置が令和9年3月31日までであることにより、令和9年4月1日（本計画の初日）から義務となる当方の整理は正しい。**一方、定めの状況を集計するのは保険者の側であり、当方は対象10事業所（認知症対応型共同生活介護7・地域密着型介護老人福祉施設3）を掲げるにとどめ、定めの状況を把握していない。</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>第1章第9節1、第5章 基本目標1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="104" customHeight="1">
+      <c r="A25" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>G23</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>多床室の室料負担は一部の類型について既に実施されていること</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>第264回 資料5 p12</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>「多床室の室料負担については、**令和7年8月より**、在宅でサービスを受ける者との負担の均衡を図るため、「その他型」及び「療養型」の介護老人保健施設並びに「Ⅱ型」の介護医療院について、**新たに室料負担を求めることとした**」。財政制度等審議会（令和8年6月26日）は「令和6年度（2024年度）介護報酬改定において室料負担の導入が見送られた類型についても、多床室の室料相当額を基本サービス費等から除外する見直しを実施することが考えられる」と指摘している。</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>**当方は「検討されています」と書くにとどめ、令和7年8月から一部の類型で既に実施されていることを書いていなかった。**区域内には介護老人保健施設3施設（定員240人）及び介護医療院があり、類型ごとの対象は確認できていない。室料負担は利用者負担であり給付費とは別のものである。</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>第1章第9節5・6、第6章第7節</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="104" customHeight="1">
+      <c r="A26" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>G24</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>介護事故の防止における市町村の役割</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>第263回 資料3 p51</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>論点②（介護現場における事故防止の推進）において、国・都道府県・市町村の役割として「**市町村：事故が発生した事業所からの報告の受付、報告内容の集計・傾向把握**」「都道府県：報告内容の広域的な集計・傾向把握、市町村からの相談対応・助言等」「国：事故情報の収集（システム・DB構築）・分析・活用」が示されている。「介護サービス情報公表システム」を活用した報告のためのサブシステムの構築と報告様式の見直しが検討され、「個人が特定されうる情報の取得は行わない」こととされている。</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>**当方の計画素案に「介護事故」「事故報告」の記載が0件であった。**報告の受付及び集計を行うのは保険者の側である。</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>第5章 基本目標5、第1章第9節6</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="104" customHeight="1">
+      <c r="A27" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>G25</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>人員配置基準に係るいわゆるローカルルール</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>第263回 資料1 p47・p51</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>「市町村に対して、人員配置基準に係るいわゆるローカルルールについて、**あくまでも厚生労働省令に従う範囲内で地域の実情に応じた内容とする必要があること**、事業者から説明を求められ（た場合の対応）」が示され、「自治体ごとに異なる解釈や取扱い（いわゆるローカルルール）が行われている状況について、引き続き実態の把握」を行うこととされている。</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>当広域連合は介護保険法第78条の4第1項により地域密着型サービスの人員・設備・運営の基準を条例で定める立場であり、ローカルルールに当たり得る。当方は当該条例を受領しておらず、令和6年改正後の省令に対応しているかを確認できていない（確認事項No.95）。条例の内容を点検する際の基準となる。</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>（確認事項No.95の備考。計画素案には反映しない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="104" customHeight="1">
+      <c r="A28" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>G26</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>令和8年度介護報酬改定の施行月と内容</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>第263回 資料1 p66</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>「**令和8年度介護報酬改定において、他職種と遜色ない処遇改善に向けて、介護従事者を対象とした幅広い措置に加え、生産性向上等に取り組む事業者の介護職員を対象にした上乗せ措置を実施（令和8年6月施行）**した」。経済財政運営と改革の基本方針2026において「次期介護報酬・障害福祉サービス等報酬改定では、経営データベースの整備・活用を含め…物価の変動に適切に対応するとともに、他職種と遜色のない処遇改善の実現を図る」とされている。</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>**当方は令和8年度改定の施行の時期を「令和8年度」としていた。原典により令和8年6月施行であることが分かった。**当方の算定は令和7年度の単価で固定しており、令和8年6月施行の改定が反映されていない。単価をR7で固定することが令和8年度・令和9年度の2回分の改定を落としているという整理は原典により裏づけられた。</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>第1章第9節4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="104" customHeight="1">
+      <c r="A29" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>G21</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>意見交換会のテーマに中山間・人口減少地域関係が置かれたこと</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>第262回 資料4</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>従来の「団体ヒアリング」を発展的に見直して「令和9年度介護報酬改定に関する意見交換会」を実施するもので、テーマは①介護系居宅サービス等②居住系・施設系サービス等③医療系サービス**④中山間・人口減少地域関係**の4区分である。「令和9年度から改正法が施行されることを踏まえ、**中山間・人口減少地域に該当する自治体及び事業者等についても対象とすることとしてはどうか**」とされている。</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>中山間・人口減少地域に該当する自治体が意見を述べる場が設けられたことを示すものである。計画の記載事項ではないため計画素案には反映していない。</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>（計画素案には反映しない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="104" customHeight="1">
+      <c r="A30" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
           <t>G12</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>送迎に係る評価の見直し（短期入所生活介護・短期入所療養介護）</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>第270回 資料4 p21</t>
         </is>
       </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>対応案は「燃料費や人件費等の高騰を踏まえ、送迎に要するコストの実態に応じた送迎加算に見直してはどうか。短期入所療養介護についても同様に検討してはどうか」「共同送迎や共同委託について明確化してはどうか」。</t>
         </is>
       </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>当区域は町の区域が広く、冬期の送迎に要する時間が長い。</t>
         </is>
       </c>
-      <c r="G18" s="5" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>第6章第2節 注1-1</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="36" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="31" ht="36" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>注）反映先は計画素案に現にある章節によります。第5章は節に分かれていないため基本目標により示します。原典の記述は要点を示したものであり、原文そのままではありません。</t>
         </is>
@@ -2444,7 +3612,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A31:G31"/>
     <mergeCell ref="A2:G2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2457,7 +3625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2470,7 +3638,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>サービス見込量及び保険料への効き（12件）</t>
+          <t>サービス見込量及び保険料への効き（15件）</t>
         </is>
       </c>
     </row>
@@ -2805,30 +3973,105 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
-    <row r="18" ht="18" customHeight="1">
-      <c r="A18" s="3" t="inlineStr">
+    <row r="17" ht="44" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>地域区分の見直し（都道府県単位を基本とする広域化）</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>いずれともいえない</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>全サービス</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>構成3町はいずれもその他の地域（上乗せ割合0％）である。広域化により上乗せ割合が変わり得る。3町の区分が同じであるため広域連合として選択する余地はない</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="44" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>登録施設介護（予防）支援の創設</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>区分の間の振替</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>居宅介護支援・介護予防支援・登録施設介護（予防）支援</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
+        <is>
+          <t>施行日は公布の日から起算して3年を超えない範囲内において政令で定める日であり、令和9年4月1日ではない。区域内に住宅型有料老人ホーム9施設（定員223人）がある</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="44" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>同一建物等居住者へのサービス提供（訪問系）の見直し</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>対応案が示されていない</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>訪問介護ほか</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>全国の住宅型有料老人ホームでは要介護者のうち週21回以上訪問介護を利用する入居者が平均27.7％である。当区域の1人1月あたり利用回数は全国の1.87倍である</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>算定への影響</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="46" customHeight="1">
-      <c r="B19" s="7" t="inlineStr">
+    <row r="22" ht="46" customHeight="1">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>単価は令和7年度の実績で固定しています（据え置きの区分C）。改定率が告示された時点で再算定します。本計画は改定率1％あたり月額61円の感度を掲げています（計画素案 第6章第6節2）。</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="46" customHeight="1">
-      <c r="B20" s="7" t="inlineStr">
+    <row r="23" ht="46" customHeight="1">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>上表の向きは互いに打ち消し合うものを含みます。単価を下げる向き（長期利用減算の強化等）と上げる向き（入浴介助加算・送迎加算の単価、中山間地域の加算）が同時に検討されており、改定率としてどちらが上回るかは示されていません。</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="46" customHeight="1">
-      <c r="B21" s="7" t="inlineStr">
+    <row r="24" ht="46" customHeight="1">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>量に及ぶもの（入浴に係る特例、定期巡回の配置基準）は、いずれも区分の間の振替又は整備の条件であり、総量を大きく動かすものではありません。</t>
         </is>
@@ -2836,11 +4079,11 @@
     </row>
   </sheetData>
   <mergeCells count="5">
+    <mergeCell ref="A21:E21"/>
+    <mergeCell ref="B23:E23"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="B24:E24"/>
+    <mergeCell ref="B22:E22"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2852,7 +4095,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2864,7 +4107,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>計画素案への反映（11件）</t>
+          <t>計画素案への反映（20件）</t>
         </is>
       </c>
     </row>
@@ -2960,17 +4203,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>第2章第1節3</t>
+          <t>第1章第9節2</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>認知症高齢者の状況の注に、国が認知症又は軽度認知障害の高齢者を65歳以上の約3割としていること、本広域連合における軽度認知障害を含む割合は把握していないことを加えた［要確認］。</t>
+          <t>導入文に、有料老人ホームの登録制の施行日が公布の日から起算して2年を超えない範囲内において政令で定める日、登録施設介護（予防）支援の施行日が3年を超えない範囲内において政令で定める日であり、いずれも令和9年4月1日ではないことを加えた。改正事項の表の有料老人ホーム制度の見直しの欄にも施行日と経過措置を書いた［要確認］。</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>第268回 資料1</t>
+          <t>第262回 資料2 p22</t>
         </is>
       </c>
     </row>
@@ -2980,17 +4223,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>第1章第9節1</t>
+          <t>第6章第2節 注3</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>交通の便が悪い地域における経営の安定等を目的とする加算が特別地域加算、中山間地域等における小規模事業所加算及び中山間地域等に居住する者へのサービス提供加算の3種類であり、いずれも区分支給限度基準額の対象外であること、地域の区分が2つの告示によることを注に加えた。従前は特別地域加算のみを掲げていた［要確認］。</t>
+          <t>令和9年4月1日に新設されるとしていた記述を改め、登録施設介護（予防）支援の施行日が公布の日から起算して3年を超えない範囲内において政令で定める日であること、区域内に住宅型有料老人ホーム9施設（定員223人）があり対象となり得る方がいること、現に居宅介護支援等として給付されている方が振り替わるものとして区分の間の振替として扱い総額を増やしていないことを加えた。</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>第270回 資料5 p9、第269回 資料1 p11</t>
+          <t>第262回 資料2 p22・p37</t>
         </is>
       </c>
     </row>
@@ -3000,17 +4243,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>第6章第2節 注1-1</t>
+          <t>第2章第3節</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>短期入所生活介護の長期利用減算の見直しが2方向であること、短期入所療養介護にも長期利用に係る減算を新たに設けることが検討されていること、中山間地域等において通所介護等で入浴介助を目的とするサービスを認める特例が検討されていることを加えた。あわせて、中山間・離島その他の農村地域において積雪期等の季節による利用の受入れが他の地域よりも高い傾向にあることと、本計画が令和7年度（12か月）によっているため年間の水準としてはこれを含んでいることを加えた［要確認］。</t>
+          <t>【指定を受けない住まいと在宅サービスの関係】を新設し、同一の建物に居住する方への提供の割合が多くなるにつれて訪問の件数が増加し移動に要する時間及び距離が短くなる実態、全国の住宅型有料老人ホームにおける訪問介護の頻回利用の割合（週21回以上が平均27.7％、要介護1・2でも18.5％）、併設又は隣接の事業所がある割合（79.1％・83.4％）を掲げ、当区域の訪問介護の1人1月あたり利用回数が全国の1.87倍であることと同じ構造と考えられる旨を書いた［要確認］。</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>第270回 資料4 p11・p14・p21、第270回 資料5 p12、第270回 資料1 p15・p16</t>
+          <t>第262回 資料2 p53・p80・p87</t>
         </is>
       </c>
     </row>
@@ -3020,17 +4263,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>第6章第6節2</t>
+          <t>第1章第9節6</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>中山間地域の加算のあり方の見直しが基本的な視点に掲げられており、当広域連合が対象となる場合は単価を上げる向きに働くこと、告示を確認できていないため見込んでいないことを加えた［要確認］。</t>
+          <t>「地域区分及び多床室の室料負担」の1行を「地域区分」と「多床室の室料負担」の2行に分け、地域区分が公務員の地域手当に準拠すること、令和6年人事院勧告により都道府県単位を基本とする広域化及び7区分から5区分への見直しが示され令和9年度改定における対応が検討されていること、北海道で級地が設定されているのは札幌市のみであり構成3町はいずれもその他の地域（0％）であること、広域連合は構成市町村に適用されている区分の範囲内で選択できることを加えた［要確認］。</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>第268回 資料1、第270回 資料5 p9</t>
+          <t>第262回 資料3 p6・p7・p18</t>
         </is>
       </c>
     </row>
@@ -3040,17 +4283,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>第6章第2節（2）注2</t>
+          <t>第2章第1節3</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>認知症対応型通所介護について、請求事業所数及び受給者数が全国的に減少傾向にあることを踏まえ、地域密着型通所介護の報酬体系及び単位数を参考にしつつ基本報酬の在り方を検討することとされていることを加えた［要確認］。</t>
+          <t>認知症高齢者の状況の注に、国が認知症又は軽度認知障害の高齢者を65歳以上の約3割としていること、令和22年には計約1,200万人となり高齢者の約3.3人に1人が認知症又は軽度認知障害になると見込んでいること、本広域連合における軽度認知障害を含む割合は把握していないことを加えた［要確認］。</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>第270回 資料1 p42</t>
+          <t>第268回 資料1、第264回 資料1 p59</t>
         </is>
       </c>
     </row>
@@ -3060,17 +4303,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>第6章第2節 注2</t>
+          <t>第1章第9節1</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>夜間対応型訪問介護の経過措置の期限を「移行の猶予は令和11年3月」から、原典の中に2通りの記載があり確定していない旨に改めた。あわせて、移行を見据えた評価の内容（24時間の通報及び相談への対応の機能の確保と日中の支援の評価）を加えた。</t>
+          <t>協力医療機関について、要件を満たす協力医療機関を定めることの義務化に令和9年3月31日までの経過措置が設けられており本計画の初日から義務となること、全国における整備割合（介護老人福祉施設67.9％ほか）と定めの状況を集計していない自治体が一定程度存在することを示したうえで、保険者として対象事業所の定めの状況を令和9年3月までに把握し要件を満たしていない事業所の医療機関との調整を支援することを加えた［要協議］。</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>第269回 資料1 p15・p34</t>
+          <t>第264回 資料2 p70・p72</t>
         </is>
       </c>
     </row>
@@ -3080,17 +4323,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>第6章第4節1</t>
+          <t>第1章第9節4</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>定期巡回・随時対応型訪問介護看護について、新規開設時の訪問介護員等の配置基準の見直しと、区域外の指定を受けて複数の市町村にまたがって提供する事業所の評価の在り方が検討されていることを加えた。いずれも整備を検討する際の条件に関わる［要協議］。</t>
+          <t>令和8年度介護報酬改定の施行等の時期を「令和8年度」から「令和8年6月施行」に改め、介護従事者を対象とした幅広い措置に加え生産性向上等に取り組む事業者の介護職員を対象とした上乗せ措置が実施されていることを加えた。令和8年度の実績が年度を通じて確定した時点で改定による単価の動きを確かめることも書いた［要確認］。</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>第269回 資料1 p18、第269回 資料2 p18</t>
+          <t>第263回 資料1 p66</t>
         </is>
       </c>
     </row>
@@ -3100,22 +4343,202 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
+          <t>第5章 基本目標5、第1章第9節6</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>介護事故の防止を新設した。事業所からの事故報告の受付、報告内容の集計及び傾向の把握を行うこと、集計及び傾向の把握の結果を事業所へ還元すること、報告の受付の方法及び様式は国の検討の結果を踏まえて定めること、原因の分析及び再発の防止を目的とするもので個人を特定し得る情報は取得しないことを書いた［要協議］。**従前は介護事故に関する記載が0件であった。**</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>第263回 資料3 p51</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="76" customHeight="1">
+      <c r="A16" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>第6章第7節</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>多床室の室料負担について、令和7年8月からその他型及び療養型の介護老人保健施設並びにⅡ型の介護医療院について室料負担を求めることとされていること、導入が見送られた類型についても見直しを行うことが考えられるとの指摘がされていること、区域内に介護老人保健施設3施設（定員240人）及び介護医療院があり類型ごとの対象を確認できていないことを加えた［要確認］。第1章第9節5の表の検討の内容にも同じ内容を加えた。</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>第264回 資料5 p12</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="76" customHeight="1">
+      <c r="A17" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>第5章 基本目標5</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>BCPの把握に係る記述に、国が平時からの行政及び他の介護施設等との連携を重要としたうえで市区町村の約6割が業務継続を可能とする備えに関する助言等を行っていない状況を示していること、保険者として事業所に対する助言及び平時からの連携体制の整備に取り組むこと、災害時情報共有システムの運用についても3町及び事業所と確認することを加えた［要協議］。</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>第263回 資料4 p30・p31</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="76" customHeight="1">
+      <c r="A18" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>第1章第9節1</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>交通の便が悪い地域における経営の安定等を目的とする加算が特別地域加算、中山間地域等における小規模事業所加算及び中山間地域等に居住する者へのサービス提供加算の3種類であり、いずれも区分支給限度基準額の対象外であること、地域の区分が2つの告示によることを注に加えた。従前は特別地域加算のみを掲げていた［要確認］。</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>第270回 資料5 p9、第269回 資料1 p11</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="76" customHeight="1">
+      <c r="A19" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>第6章第2節 注1-1</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>短期入所生活介護の長期利用減算の見直しが2方向であること、短期入所療養介護にも長期利用に係る減算を新たに設けることが検討されていること、中山間地域等において通所介護等で入浴介助を目的とするサービスを認める特例が検討されていることを加えた。あわせて、中山間・離島その他の農村地域において積雪期等の季節による利用の受入れが他の地域よりも高い傾向にあることと、本計画が令和7年度（12か月）によっているため年間の水準としてはこれを含んでいることを加えた［要確認］。</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>第270回 資料4 p11・p14・p21、第270回 資料5 p12、第270回 資料1 p15・p16</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="76" customHeight="1">
+      <c r="A20" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>第6章第6節2</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>中山間地域の加算のあり方の見直しが基本的な視点に掲げられており、当広域連合が対象となる場合は単価を上げる向きに働くこと、告示を確認できていないため見込んでいないことを加えた［要確認］。</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>第268回 資料1、第270回 資料5 p9</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="76" customHeight="1">
+      <c r="A21" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>第6章第2節（2）注2</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>認知症対応型通所介護について、請求事業所数及び受給者数が全国的に減少傾向にあることを踏まえ、地域密着型通所介護の報酬体系及び単位数を参考にしつつ基本報酬の在り方を検討することとされていることを加えた［要確認］。</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>第270回 資料1 p42</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="76" customHeight="1">
+      <c r="A22" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>第6章第2節 注2</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>夜間対応型訪問介護の経過措置の期限を「移行の猶予は令和11年3月」から、原典の中に2通りの記載があり確定していない旨に改めた。あわせて、移行を見据えた評価の内容（24時間の通報及び相談への対応の機能の確保と日中の支援の評価）を加えた。</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>第269回 資料1 p15・p34</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="76" customHeight="1">
+      <c r="A23" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>第6章第4節1</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>定期巡回・随時対応型訪問介護看護について、新規開設時の訪問介護員等の配置基準の見直しと、区域外の指定を受けて複数の市町村にまたがって提供する事業所の評価の在り方が検討されていることを加えた。いずれも整備を検討する際の条件に関わる［要協議］。</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>第269回 資料1 p18、第269回 資料2 p18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="76" customHeight="1">
+      <c r="A24" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
           <t>第6章第5節</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>通所リハビリテーションの退院時共同指導加算の対象に介護老人保健施設及び介護医療院の退所者を加えることが検討されていることを加えた。</t>
         </is>
       </c>
-      <c r="D15" s="5" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>第270回 資料3 p22</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="36" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
         <is>
           <t>注）反映先は計画素案に現にある章節によります。単位数、算定の要件及び施行の時期は書いていません。いずれも検討されている段階のものであるため［要確認］又は［要協議］を付しています。</t>
         </is>
@@ -3123,7 +4546,7 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A25:D25"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3277,7 +4700,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>第256回〜第267回の資料</t>
+          <t>第256回〜第261回、第265回〜第267回の資料</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
@@ -3287,7 +4710,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>社内の整理（原典の要約）による。本文を原典で確認していない。</t>
+          <t>社内の整理（原典の要約）による。本文を原典で確認していない。第265回から第267回は団体等の意見交換の回である。</t>
         </is>
       </c>
     </row>
@@ -3383,7 +4806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3447,7 +4870,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>11件・311頁</t>
+          <t>25件・1037頁（第262・第263・第264・第268・第269・第270回）</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -3472,7 +4895,7 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>第268・第269・第270回</t>
+          <t>第262・第263・第264・第268・第269・第270回</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -3522,7 +4945,7 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>7件</t>
+          <t>11件</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -3783,21 +5206,21 @@
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="9" t="n">
-        <v>15</v>
+        <v>14.1</v>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>計画素案に単位数の値を書いていないこと</t>
+          <t>登録施設介護（予防）支援を令和9年4月1日に新設されるものとしていないこと</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>数値を伴う「○○単位」の走査</t>
+          <t>素案の走査</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>現れない</t>
+          <t>「令和9年4月1日に新設される登録施設介護」 0件</t>
         </is>
       </c>
       <c r="E19" s="14" t="inlineStr">
@@ -3808,21 +5231,21 @@
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="9" t="n">
-        <v>16</v>
+        <v>14.2</v>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>確認事項No.182が台帳にあり未決であること</t>
+          <t>登録制及び登録施設介護（予防）支援の施行日が素案に入ったこと</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>台帳の照合</t>
+          <t>素案の走査</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>台帳にあり・未決</t>
+          <t>3年を超えない 2件／2年を超えない 2件</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">
@@ -3833,21 +5256,21 @@
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="9" t="n">
-        <v>17</v>
+        <v>14.3</v>
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>本文未確認の解消の判定が整理の記載と対応すること</t>
+          <t>地域区分の広域連合ルールと広域化が素案に入ったこと</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>件数の照合</t>
+          <t>素案の走査</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>整理 3件／本表 3件</t>
+          <t>第1章第9節</t>
         </is>
       </c>
       <c r="E21" s="14" t="inlineStr">
@@ -3858,21 +5281,21 @@
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="9" t="n">
-        <v>18</v>
+        <v>14.4</v>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>効きの向きがいずれも記されていること</t>
+          <t>構成3町の地域区分がその他の地域であることを書いていること</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>欄の走査</t>
+          <t>素案の走査</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>12件</t>
+          <t>第1章第9節</t>
         </is>
       </c>
       <c r="E22" s="14" t="inlineStr">
@@ -3883,21 +5306,21 @@
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="9" t="n">
-        <v>19</v>
+        <v>14.5</v>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>当方の内部の仕組み・作業経過の語が現れないこと</t>
+          <t>同一建物等居住者へのサービス提供の実態が素案に入ったこと</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>語の走査</t>
+          <t>素案の走査</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>現れない</t>
+          <t>第2章第3節</t>
         </is>
       </c>
       <c r="E23" s="14" t="inlineStr">
@@ -3908,21 +5331,21 @@
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="9" t="n">
-        <v>20</v>
+        <v>14.6</v>
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>禁止表現が現れないこと</t>
+          <t>業務継続に係る行政の役割が素案に入ったこと</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>語の走査</t>
+          <t>素案の走査</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>現れない</t>
+          <t>第5章</t>
         </is>
       </c>
       <c r="E24" s="14" t="inlineStr">
@@ -3933,31 +5356,306 @@
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="9" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>認知症又は軽度認知障害の将来の見通しが素案に入ったこと</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>素案の走査</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>第2章第1節</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="9" t="n">
+        <v>14.96</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>令和8年度介護報酬改定の施行月が素案に入ったこと</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>素案の走査</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>第1章第9節</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="9" t="n">
+        <v>14.95</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>介護事故の防止が素案に入ったこと</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>素案の走査</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>第5章／第1章第9節</t>
+        </is>
+      </c>
+      <c r="E27" s="14" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="9" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>多床室の室料負担が令和7年8月から一部の類型で実施されていることを素案に書いたこと</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>素案の走査</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>第1章第9節／第6章第7節</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="9" t="n">
+        <v>14.8</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>協力医療機関の経過措置の期限と定めの状況の把握が素案に入ったこと</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>素案の走査</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>令和9年3月31日までの経過措置 1件／定めの状況 1件</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>計画素案に単位数の値を書いていないこと</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>数値を伴う「○○単位」の走査</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>現れない</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="9" t="n">
+        <v>16</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>確認事項No.182が台帳にあり未決であること</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>台帳の照合</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>台帳にあり・未決</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>本文未確認の解消の判定が整理の記載と対応すること</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>件数の照合</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>整理 3件／本表 3件</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>効きの向きがいずれも記されていること</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>欄の走査</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>15件</t>
+        </is>
+      </c>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="9" t="n">
+        <v>19</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>当方の内部の仕組み・作業経過の語が現れないこと</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>語の走査</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>現れない</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>禁止表現が現れないこと</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>語の走査</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>現れない</t>
+        </is>
+      </c>
+      <c r="E35" s="14" t="inlineStr">
+        <is>
+          <t>適合</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="30" customHeight="1">
+      <c r="A36" s="9" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>個人情報の形（電話番号・メールアドレス）が現れないこと</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>正規表現</t>
         </is>
       </c>
-      <c r="D25" s="5" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>0件</t>
         </is>
       </c>
-      <c r="E25" s="14" t="inlineStr">
+      <c r="E36" s="14" t="inlineStr">
         <is>
           <t>適合</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+    <row r="38" ht="30" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
         <is>
           <t>注）本表は、受領した資料のうち確認に要する箇所を読んで作成したものです。</t>
         </is>
@@ -3966,7 +5664,7 @@
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A38:E38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/第10期計画_介護給付費分科会資料（原典）の受領点検.xlsx
+++ b/output/第10期計画_介護給付費分科会資料（原典）の受領点検.xlsx
@@ -2719,7 +2719,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>協議会を設置するのは北海道であり、当広域連合及び構成3町はこれに参画し、又はその支援を受ける立場となる。当方の整理（第1章第9節2の改正事項）に本件が入っていなかった。</t>
+          <t>協議会を置くのは北海道である。当方の整理（第1章第9節2の改正事項）に本件が入っていなかった。なお同日に受領した社会福祉法等の一部を改正する法律案要綱 第2の15は、本協議会を介護保険法第120条の3の「協議会」とし、その目的を「質の高い介護サービスの提供の確保とその提供のための安定した経営基盤の確立の双方の実現を図る取組の促進」とし、構成員に市町村を含むものとしている。本資料の「生産性向上推進のための協議会」は分科会資料の表現であり、計画素案には法律の定めによる記述を用いた。</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
@@ -4148,12 +4148,12 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>改正事項の表に「介護人材の確保及び生産性向上の推進」を加えた。人材確保及び生産性向上の取組の推進が国及び都道府県の責務とされ、生産性向上推進のための協議会の設置が都道府県の義務とされたこと。協議会を設置するのは北海道であり、本広域連合及び構成3町はこれに参画し、又は支援を受ける立場であることを記した［要確認］。</t>
+          <t>改正事項の表に「介護人材の確保及び生産性向上の推進」を加えた。人材確保及び生産性向上の取組の推進が国及び都道府県の責務とされ、協議会の設置が都道府県の義務とされたこと。同日に受領した法律案要綱により、本協議会が介護保険法第120条の3の協議会であり構成員に市町村を含むことが分かったため、協議会を置くのは北海道であり市町村は構成員として参画するものとされていることを記した［要協議］。</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>第268回 資料1</t>
+          <t>第268回 資料1、法律案要綱 第2の15</t>
         </is>
       </c>
     </row>
@@ -5085,7 +5085,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>生産性向上推進のための協議会が素案に入ったこと</t>
+          <t>協議会（法第120条の3）が素案に入り、市町村が構成員であることを書いていること</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>3年を超えない 2件／2年を超えない 2件</t>
+          <t>3年を超えない 3件／2年を超えない 3件</t>
         </is>
       </c>
       <c r="E20" s="14" t="inlineStr">

--- a/output/第10期計画_介護給付費分科会資料（原典）の受領点検.xlsx
+++ b/output/第10期計画_介護給付費分科会資料（原典）の受領点検.xlsx
@@ -3174,7 +3174,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>**当方は計画素案に「令和9年4月1日に新設される登録施設介護（予防）支援」と書いていた。** 改正法の施行は原則として令和9年4月1日であるが、登録制及び登録施設介護（予防）支援はこれに当たらない。区域内には住宅型有料老人ホーム9施設（定員223人）があり、登録施設介護（予防）支援の対象となり得る方がいる。</t>
+          <t>当方は計画素案に「令和9年4月1日に新設される登録施設介護（予防）支援」と書いていた。 改正法の施行は原則として令和9年4月1日であるが、登録制及び登録施設介護（予防）支援はこれに当たらない。区域内には住宅型有料老人ホーム9施設（定員223人）があり、登録施設介護（予防）支援の対象となり得る方がいる。</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -3209,7 +3209,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>当区域の訪問介護の1人1月あたり利用回数は全国の1.87倍であり、訪問介護13事業所のうち8事業所が住まいに併設している。**当方の仮説（指定を受けない住まいの入居者への訪問による）は国の資料が示す実態と同じ向きである。**同一の建物に居住する方への提供の割合は把握していない。</t>
+          <t>当区域の訪問介護の1人1月あたり利用回数は全国の1.87倍であり、訪問介護13事業所のうち8事業所が住まいに併設している。当方の仮説（指定を受けない住まいの入居者への訪問による）は国の資料が示す実態と同じ向きである。同一の建物に居住する方への提供の割合は把握していない。</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -3239,12 +3239,12 @@
       </c>
       <c r="E20" s="5" t="inlineStr">
         <is>
-          <t>地域区分の特例に「ウ　**広域連合については、構成自治体に適用されている区分の範囲内で選択することを認めている**」がある（広域連合ルール）。また「国家公務員の地域手当については、令和6年人事院勧告において、級地区分を設定する地域の単位を広域化（従来の市町村単位から都道府県単位を基本）するとともに、級地区分の段階数を7区分から5区分とする見直し内容が示され」たことを踏まえ、「令和9年度介護報酬改定における対応についてどのように考えるか」が論点とされている。令和6年度から令和8年度までの適用地域の表において、北海道で級地が設定されているのは札幌市のみである。</t>
+          <t>地域区分の特例に「ウ　広域連合については、構成自治体に適用されている区分の範囲内で選択することを認めている」がある（広域連合ルール）。また「国家公務員の地域手当については、令和6年人事院勧告において、級地区分を設定する地域の単位を広域化（従来の市町村単位から都道府県単位を基本）するとともに、級地区分の段階数を7区分から5区分とする見直し内容が示され」たことを踏まえ、「令和9年度介護報酬改定における対応についてどのように考えるか」が論点とされている。令和6年度から令和8年度までの適用地域の表において、北海道で級地が設定されているのは札幌市のみである。</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>**構成3町はいずれも表に現れず、その他の地域（上乗せ割合0％）である。**3町の区分が同じであるため、現時点では広域連合として選択する余地はない。都道府県単位を基本とする広域化が行われる場合は上乗せ割合が変わり得るため、単価に及ぶ。当方は地域区分について「令和7年度の実績に含まれています」と書くにとどめていた。</t>
+          <t>構成3町はいずれも表に現れず、その他の地域（上乗せ割合0％）である。3町の区分が同じであるため、現時点では広域連合として選択する余地はない。都道府県単位を基本とする広域化が行われる場合は上乗せ割合が変わり得るため、単価に及ぶ。当方は地域区分について「令和7年度の実績に含まれています」と書くにとどめていた。</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -3274,12 +3274,12 @@
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>「BCPの実効性を高めるためには、行政や他の介護施設等との平時からの連携が重要と考えられるが、…**市区町村においても介護事業所等に対して、業務継続を可能とする備えに関する助言等を約6割が行っていない状況**にあり、平時における行政や近隣の法人等の連携体制の整備が課題となっている」。「災害時情報共有システムを知らない施設等が2割あり、運用に関する取組を行っていない施設等も3割ある」。論点は「災害対策基本法等の改正などを踏まえた災害発生時に備えた平時からの行政や他の介護施設等との連携による体制整備を促進するための方策」である。</t>
+          <t>「BCPの実効性を高めるためには、行政や他の介護施設等との平時からの連携が重要と考えられるが、…市区町村においても介護事業所等に対して、業務継続を可能とする備えに関する助言等を約6割が行っていない状況にあり、平時における行政や近隣の法人等の連携体制の整備が課題となっている」。「災害時情報共有システムを知らない施設等が2割あり、運用に関する取組を行っていない施設等も3割ある」。論点は「災害対策基本法等の改正などを踏まえた災害発生時に備えた平時からの行政や他の介護施設等との連携による体制整備を促進するための方策」である。</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>**助言等を行うのは保険者及び構成3町の側である。**当方の素案はBCPの策定率・訓練・相互応援協定の把握を掲げていたが、行政の側の役割（助言・平時からの連携体制の整備・災害時情報共有システムの運用）に触れていなかった。</t>
+          <t>助言等を行うのは保険者及び構成3町の側である。当方の素案はBCPの策定率・訓練・相互応援協定の把握を掲げていたが、行政の側の役割（助言・平時からの連携体制の整備・災害時情報共有システムの運用）に触れていなかった。</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>「認知症高齢者数は、令和4年で約443万人、軽度認知障害（MCI）高齢者数は約559万人と推計され、その合計は1,000万人を超える状況にある。また、**令和22年にはその人数が約1,200万人（認知症約584万人、MCI約613万人）となり、高齢者の約3.3人に1人が認知症又はMCIになると見込まれる**」。「独居認知症高齢者と独居MCI高齢者を合算した独居認知機能低下高齢者は、2025年の段階で250万人、2050年には349万人になると推計」。「令和2年調査における若年性認知症の人の数は約3.6万人」。</t>
+          <t>「認知症高齢者数は、令和4年で約443万人、軽度認知障害（MCI）高齢者数は約559万人と推計され、その合計は1,000万人を超える状況にある。また、令和22年にはその人数が約1,200万人（認知症約584万人、MCI約613万人）となり、高齢者の約3.3人に1人が認知症又はMCIになると見込まれる」。「独居認知症高齢者と独居MCI高齢者を合算した独居認知機能低下高齢者は、2025年の段階で250万人、2050年には349万人になると推計」。「令和2年調査における若年性認知症の人の数は約3.6万人」。</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
@@ -3344,7 +3344,7 @@
       </c>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>論点は「特に夜間の見守り機器の活用による職員の業務時間の削減等が見られたことを踏まえ、夜間の見守り機器を活用した場合の方策」と、「令和6年に新設した施設系サービスの生産性向上推進体制加算について先進的な取組への評価のあり方や訪問系・通所系サービスの生産性向上の取組の評価等」、及び「地域の実情等を踏まえた**経営の協働化・大規模化の推進**」である。</t>
+          <t>論点は「特に夜間の見守り機器の活用による職員の業務時間の削減等が見られたことを踏まえ、夜間の見守り機器を活用した場合の方策」と、「令和6年に新設した施設系サービスの生産性向上推進体制加算について先進的な取組への評価のあり方や訪問系・通所系サービスの生産性向上の取組の評価等」、及び「地域の実情等を踏まえた経営の協働化・大規模化の推進」である。</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="E24" s="5" t="inlineStr">
         <is>
-          <t>「令和6年度介護報酬改定において、高齢者施設等に一定の要件を満たす協力医療機関の設定を義務付け、**令和9年3月31日までの経過措置**を設けている」。「協力医療機関の要件を満たす体制の整備割合は、介護老人福祉施設は67.9％、介護老人保健施設は83.3％、介護医療院は84.9％、養護老人ホームは60.4％であり、また、**定めの状況について、集計していないと回答した自治体が一定程度存在し、定めの状況には地域差が見られた**」。協力医療機関となることを断った理由として「常時診療を行う体制の確保が困難」等が挙げられている。令和8年度改定検証調査の速報値は令和8年秋頃に示される予定。</t>
+          <t>「令和6年度介護報酬改定において、高齢者施設等に一定の要件を満たす協力医療機関の設定を義務付け、令和9年3月31日までの経過措置を設けている」。「協力医療機関の要件を満たす体制の整備割合は、介護老人福祉施設は67.9％、介護老人保健施設は83.3％、介護医療院は84.9％、養護老人ホームは60.4％であり、また、定めの状況について、集計していないと回答した自治体が一定程度存在し、定めの状況には地域差が見られた」。協力医療機関となることを断った理由として「常時診療を行う体制の確保が困難」等が挙げられている。令和8年度改定検証調査の速報値は令和8年秋頃に示される予定。</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>**経過措置が令和9年3月31日までであることにより、令和9年4月1日（本計画の初日）から義務となる当方の整理は正しい。**一方、定めの状況を集計するのは保険者の側であり、当方は対象10事業所（認知症対応型共同生活介護7・地域密着型介護老人福祉施設3）を掲げるにとどめ、定めの状況を把握していない。</t>
+          <t>経過措置が令和9年3月31日までであることにより、令和9年4月1日（本計画の初日）から義務となる当方の整理は正しい。一方、定めの状況を集計するのは保険者の側であり、当方は対象10事業所（認知症対応型共同生活介護7・地域密着型介護老人福祉施設3）を掲げるにとどめ、定めの状況を把握していない。</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>「多床室の室料負担については、**令和7年8月より**、在宅でサービスを受ける者との負担の均衡を図るため、「その他型」及び「療養型」の介護老人保健施設並びに「Ⅱ型」の介護医療院について、**新たに室料負担を求めることとした**」。財政制度等審議会（令和8年6月26日）は「令和6年度（2024年度）介護報酬改定において室料負担の導入が見送られた類型についても、多床室の室料相当額を基本サービス費等から除外する見直しを実施することが考えられる」と指摘している。</t>
+          <t>「多床室の室料負担については、令和7年8月より、在宅でサービスを受ける者との負担の均衡を図るため、「その他型」及び「療養型」の介護老人保健施設並びに「Ⅱ型」の介護医療院について、新たに室料負担を求めることとした」。財政制度等審議会（令和8年6月26日）は「令和6年度（2024年度）介護報酬改定において室料負担の導入が見送られた類型についても、多床室の室料相当額を基本サービス費等から除外する見直しを実施することが考えられる」と指摘している。</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>**当方は「検討されています」と書くにとどめ、令和7年8月から一部の類型で既に実施されていることを書いていなかった。**区域内には介護老人保健施設3施設（定員240人）及び介護医療院があり、類型ごとの対象は確認できていない。室料負担は利用者負担であり給付費とは別のものである。</t>
+          <t>当方は「検討されています」と書くにとどめ、令和7年8月から一部の類型で既に実施されていることを書いていなかった。区域内には介護老人保健施設3施設（定員240人）及び介護医療院があり、類型ごとの対象は確認できていない。室料負担は利用者負担であり給付費とは別のものである。</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>論点②（介護現場における事故防止の推進）において、国・都道府県・市町村の役割として「**市町村：事故が発生した事業所からの報告の受付、報告内容の集計・傾向把握**」「都道府県：報告内容の広域的な集計・傾向把握、市町村からの相談対応・助言等」「国：事故情報の収集（システム・DB構築）・分析・活用」が示されている。「介護サービス情報公表システム」を活用した報告のためのサブシステムの構築と報告様式の見直しが検討され、「個人が特定されうる情報の取得は行わない」こととされている。</t>
+          <t>論点②（介護現場における事故防止の推進）において、国・都道府県・市町村の役割として「市町村：事故が発生した事業所からの報告の受付、報告内容の集計・傾向把握」「都道府県：報告内容の広域的な集計・傾向把握、市町村からの相談対応・助言等」「国：事故情報の収集（システム・DB構築）・分析・活用」が示されている。「介護サービス情報公表システム」を活用した報告のためのサブシステムの構築と報告様式の見直しが検討され、「個人が特定されうる情報の取得は行わない」こととされている。</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>**当方の計画素案に「介護事故」「事故報告」の記載が0件であった。**報告の受付及び集計を行うのは保険者の側である。</t>
+          <t>当方の計画素案に「介護事故」「事故報告」の記載が0件であった。報告の受付及び集計を行うのは保険者の側である。</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>「市町村に対して、人員配置基準に係るいわゆるローカルルールについて、**あくまでも厚生労働省令に従う範囲内で地域の実情に応じた内容とする必要があること**、事業者から説明を求められ（た場合の対応）」が示され、「自治体ごとに異なる解釈や取扱い（いわゆるローカルルール）が行われている状況について、引き続き実態の把握」を行うこととされている。</t>
+          <t>「市町村に対して、人員配置基準に係るいわゆるローカルルールについて、あくまでも厚生労働省令に従う範囲内で地域の実情に応じた内容とする必要があること、事業者から説明を求められ（た場合の対応）」が示され、「自治体ごとに異なる解釈や取扱い（いわゆるローカルルール）が行われている状況について、引き続き実態の把握」を行うこととされている。</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
@@ -3519,12 +3519,12 @@
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>「**令和8年度介護報酬改定において、他職種と遜色ない処遇改善に向けて、介護従事者を対象とした幅広い措置に加え、生産性向上等に取り組む事業者の介護職員を対象にした上乗せ措置を実施（令和8年6月施行）**した」。経済財政運営と改革の基本方針2026において「次期介護報酬・障害福祉サービス等報酬改定では、経営データベースの整備・活用を含め…物価の変動に適切に対応するとともに、他職種と遜色のない処遇改善の実現を図る」とされている。</t>
+          <t>「令和8年度介護報酬改定において、他職種と遜色ない処遇改善に向けて、介護従事者を対象とした幅広い措置に加え、生産性向上等に取り組む事業者の介護職員を対象にした上乗せ措置を実施（令和8年6月施行）した」。経済財政運営と改革の基本方針2026において「次期介護報酬・障害福祉サービス等報酬改定では、経営データベースの整備・活用を含め…物価の変動に適切に対応するとともに、他職種と遜色のない処遇改善の実現を図る」とされている。</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>**当方は令和8年度改定の施行の時期を「令和8年度」としていた。原典により令和8年6月施行であることが分かった。**当方の算定は令和7年度の単価で固定しており、令和8年6月施行の改定が反映されていない。単価をR7で固定することが令和8年度・令和9年度の2回分の改定を落としているという整理は原典により裏づけられた。</t>
+          <t>当方は令和8年度改定の施行の時期を「令和8年度」としていた。原典により令和8年6月施行であることが分かった。当方の算定は令和7年度の単価で固定しており、令和8年6月施行の改定が反映されていない。単価をR7で固定することが令和8年度・令和9年度の2回分の改定を落としているという整理は原典により裏づけられた。</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>従来の「団体ヒアリング」を発展的に見直して「令和9年度介護報酬改定に関する意見交換会」を実施するもので、テーマは①介護系居宅サービス等②居住系・施設系サービス等③医療系サービス**④中山間・人口減少地域関係**の4区分である。「令和9年度から改正法が施行されることを踏まえ、**中山間・人口減少地域に該当する自治体及び事業者等についても対象とすることとしてはどうか**」とされている。</t>
+          <t>従来の「団体ヒアリング」を発展的に見直して「令和9年度介護報酬改定に関する意見交換会」を実施するもので、テーマは①介護系居宅サービス等②居住系・施設系サービス等③医療系サービス④中山間・人口減少地域関係の4区分である。「令和9年度から改正法が施行されることを踏まえ、中山間・人口減少地域に該当する自治体及び事業者等についても対象とすることとしてはどうか」とされている。</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>介護事故の防止を新設した。事業所からの事故報告の受付、報告内容の集計及び傾向の把握を行うこと、集計及び傾向の把握の結果を事業所へ還元すること、報告の受付の方法及び様式は国の検討の結果を踏まえて定めること、原因の分析及び再発の防止を目的とするもので個人を特定し得る情報は取得しないことを書いた［要協議］。**従前は介護事故に関する記載が0件であった。**</t>
+          <t>介護事故の防止を新設した。事業所からの事故報告の受付、報告内容の集計及び傾向の把握を行うこと、集計及び傾向の把握の結果を事業所へ還元すること、報告の受付の方法及び様式は国の検討の結果を踏まえて定めること、原因の分析及び再発の防止を目的とするもので個人を特定し得る情報は取得しないことを書いた［要協議］。従前は介護事故に関する記載が0件であった。</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">

--- a/output/第10期計画_介護給付費分科会資料（原典）の受領点検.xlsx
+++ b/output/第10期計画_介護給付費分科会資料（原典）の受領点検.xlsx
@@ -5470,7 +5470,7 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>令和9年3月31日までの経過措置 1件／定めの状況 1件</t>
+          <t>令和9年3月31日までの経過措置 1件／定めの状況 2件</t>
         </is>
       </c>
       <c r="E29" s="14" t="inlineStr">
